--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T15:15:02+00:00</t>
+    <t>2026-02-06T13:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T13:40:54+00:00</t>
+    <t>2026-02-06T14:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T15:19:47+00:00</t>
+    <t>2026-02-25T14:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T14:12:38+00:00</t>
+    <t>2026-02-26T10:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:50:19+00:00</t>
+    <t>2026-02-26T16:06:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:06:51+00:00</t>
+    <t>2026-02-27T10:48:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:48:32+00:00</t>
+    <t>2026-02-27T17:34:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T17:34:14+00:00</t>
+    <t>2026-03-02T09:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T09:04:22+00:00</t>
+    <t>2026-03-02T10:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T10:45:03+00:00</t>
+    <t>2026-03-02T11:00:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T11:00:56+00:00</t>
+    <t>2026-03-16T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:16:38+00:00</t>
+    <t>2026-03-16T15:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:31:45+00:00</t>
+    <t>2026-03-17T17:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T17:41:27+00:00</t>
+    <t>2026-04-09T09:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T09:33:58+00:00</t>
+    <t>2026-05-07T09:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T09:37:23+00:00</t>
+    <t>2026-06-10T13:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T13:07:20+00:00</t>
+    <t>2026-06-16T08:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:06:32+00:00</t>
+    <t>2026-06-16T08:52:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:52:34+00:00</t>
+    <t>2026-06-16T09:33:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T09:33:33+00:00</t>
+    <t>2026-06-16T10:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:35:13+00:00</t>
+    <t>2026-06-16T10:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:46:14+00:00</t>
+    <t>2026-06-16T11:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T11:08:56+00:00</t>
+    <t>2026-06-16T14:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:39:41+00:00</t>
+    <t>2026-06-16T16:50:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:50:35+00:00</t>
+    <t>2026-06-17T09:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:02:27+00:00</t>
+    <t>2026-06-17T09:20:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:20:14+00:00</t>
+    <t>2026-06-29T13:11:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:11:00+00:00</t>
+    <t>2026-06-30T08:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>7</t>
+    <t>11</t>
   </si>
   <si>
     <t>Level</t>
@@ -181,6 +181,30 @@
   </si>
   <si>
     <t>Permet de compléter ou éclairer la description de l'attente.</t>
+  </si>
+  <si>
+    <t>demandeOrientation</t>
+  </si>
+  <si>
+    <t>Pièce jointe composant la demande d'orientation.</t>
+  </si>
+  <si>
+    <t>depotPoste</t>
+  </si>
+  <si>
+    <t>Preuve du dépôt de la poste.</t>
+  </si>
+  <si>
+    <t>reponseOrientation</t>
+  </si>
+  <si>
+    <t>Réponse de la CDAPH à la demande d'orientation.</t>
+  </si>
+  <si>
+    <t>pieceComplementaire</t>
+  </si>
+  <si>
+    <t>Pièce(s) complémentaire(s) à la demande d'orientation.</t>
   </si>
 </sst>
 </file>
@@ -492,7 +516,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -593,6 +617,54 @@
       </c>
       <c r="D8" s="2"/>
     </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:27:53+00:00</t>
+    <t>2026-06-30T13:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:41:45+00:00</t>
+    <t>2026-06-30T14:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:01:12+00:00</t>
+    <t>2026-06-30T14:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:55:37+00:00</t>
+    <t>2026-07-01T09:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T09:47:49+00:00</t>
+    <t>2026-07-01T11:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:47:31+00:00</t>
+    <t>2026-07-01T13:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:17:54+00:00</t>
+    <t>2026-07-01T14:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:33:44+00:00</t>
+    <t>2026-07-01T14:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:55:22+00:00</t>
+    <t>2026-07-01T15:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:33:30+00:00</t>
+    <t>2026-07-20T07:42:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.4.0-ballot</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:42:46+00:00</t>
+    <t>2026-07-22T13:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-discriminator.xlsx
+++ b/main/ig/CodeSystem-tddui-discriminator.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:04:03+00:00</t>
+    <t>2026-07-22T14:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
